--- a/Real-Estate-Valuation-all-in-one-calculator.xlsx
+++ b/Real-Estate-Valuation-all-in-one-calculator.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hongy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hongy\Downloads\gumroad交付品上架管理\直接放github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8734287B-6C66-4A64-827E-6E15D40AFFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D7514E-D417-4C74-B5B3-7010061616B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -227,7 +227,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="118">
   <si>
     <t>Real Estate Operations Financial Model</t>
   </si>
@@ -580,16 +580,6 @@
     <t>MONTHLY CASH FLOW  —  Cumulative vs. In/Outflows</t>
   </si>
   <si>
-    <t>SENSITIVITY MATRIX  —  Equity IRR  x  Sale Value (rows)  x  Capex Cost (columns)</t>
-  </si>
-  <si>
-    <t>[ MANUAL BUILD REQUIRED — see note below ]</t>
-  </si>
-  <si>
-    <t>This grid is NOT populated because a faithful per-cell recompute requires the entire calculation engine (incl. the SCAN-based revolving credit chain) to be callable as a single parametrized function -- e.g. one master named LAMBDA that takes (sale_price, capex_budget) and returns Equity IRR, driven across the grid via MAKEARRAY. That is a substantial, separable refactor of Sheet 03, not an incremental addition -- attempting a shortcut (e.g. a linear approximation that ignores revolving-credit timing effects) would misrepresent the model, which is exactly what you asked NOT to do. Source data (GROSS_SALE_PRICE, CAPEX_TOTAL_BUDGET named ranges) is already isolated and ready to be swapped by a MAKEARRAY wrapper if you want this built as a dedicated follow-up.
-Suggested axis ranges once built: Sale Value +/-15% around GROSS_SALE_PRICE (7 steps) x Capex Cost +/-20% around CAPEX_TOTAL_BUDGET (7 steps).</t>
-  </si>
-  <si>
     <t>NOTE: The four multiplier rows above (Capex/Sale/Rent/Rate) are a reasonable, minimal instantiation covering every driver referenced elsewhere in the spec. Extend this block with additional rows if your real scenarios need more drivers -- the XLOOKUP pattern scales to any row count without touching downstream formulas.</t>
   </si>
 </sst>
@@ -603,7 +593,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -679,13 +669,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF888888"/>
@@ -713,7 +696,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -747,12 +730,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE5F4FA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF888888"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -829,7 +806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -855,34 +832,7 @@
     <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -891,6 +841,30 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2995,12 +2969,12 @@
       <c r="I3" s="20"/>
     </row>
     <row r="5" spans="2:9" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
@@ -3015,12 +2989,12 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B9" s="1" t="s">
@@ -3035,14 +3009,14 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B13" s="4" t="s">
@@ -3166,46 +3140,46 @@
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B25" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
+      <c r="B25" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3234,7 +3208,7 @@
     <tabColor rgb="FF051C2C"/>
   </sheetPr>
   <dimension ref="B2:DS51"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.73046875" customWidth="1"/>
     <col min="2" max="2" width="34.73046875" customWidth="1"/>
@@ -3249,7 +3223,7 @@
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
     </row>
-    <row r="3" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B3" s="20" t="s">
         <v>20</v>
       </c>
@@ -3257,13 +3231,13 @@
       <c r="D3" s="20"/>
     </row>
     <row r="5" spans="2:4" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
     </row>
-    <row r="7" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
         <v>22</v>
       </c>
@@ -3274,7 +3248,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B8" s="5" t="s">
         <v>24</v>
       </c>
@@ -3285,7 +3259,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B9" s="5" t="s">
         <v>26</v>
       </c>
@@ -3297,25 +3271,24 @@
       </c>
     </row>
     <row r="10" spans="2:4" ht="50.65" x14ac:dyDescent="0.4">
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="17">
         <v>11500000</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="13.9" x14ac:dyDescent="0.4"/>
     <row r="12" spans="2:4" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
     </row>
-    <row r="14" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
@@ -3326,7 +3299,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B15" s="5" t="s">
         <v>33</v>
       </c>
@@ -3337,7 +3310,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="5" t="s">
         <v>35</v>
       </c>
@@ -3349,13 +3322,13 @@
       </c>
     </row>
     <row r="18" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
     </row>
-    <row r="20" spans="2:123" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B20" s="5" t="s">
         <v>38</v>
       </c>
@@ -3723,7 +3696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:123" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B21" s="5" t="s">
         <v>39</v>
       </c>
@@ -3733,13 +3706,13 @@
       </c>
     </row>
     <row r="23" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
     </row>
-    <row r="25" spans="2:123" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B25" s="5" t="s">
         <v>41</v>
       </c>
@@ -3750,7 +3723,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="2:123" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B26" s="5" t="s">
         <v>43</v>
       </c>
@@ -3761,7 +3734,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="2:123" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B27" s="5" t="s">
         <v>45</v>
       </c>
@@ -3773,13 +3746,13 @@
       </c>
     </row>
     <row r="29" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
     </row>
-    <row r="31" spans="2:123" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B31" s="5" t="s">
         <v>48</v>
       </c>
@@ -3790,18 +3763,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="2:123" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B32" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="18">
         <v>1</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" s="5" t="s">
         <v>52</v>
       </c>
@@ -3812,7 +3785,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" s="5" t="s">
         <v>54</v>
       </c>
@@ -3824,13 +3797,13 @@
       </c>
     </row>
     <row r="36" spans="2:4" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
     </row>
-    <row r="38" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B38" s="5" t="s">
         <v>57</v>
       </c>
@@ -3841,7 +3814,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B39" s="5" t="s">
         <v>59</v>
       </c>
@@ -3853,13 +3826,13 @@
       </c>
     </row>
     <row r="41" spans="2:4" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
     </row>
-    <row r="43" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B43" s="5" t="s">
         <v>62</v>
       </c>
@@ -3871,17 +3844,17 @@
       </c>
     </row>
     <row r="44" spans="2:4" ht="30.4" x14ac:dyDescent="0.4">
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="17">
         <v>42000</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B45" s="5" t="s">
         <v>66</v>
       </c>
@@ -3892,7 +3865,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B46" s="5" t="s">
         <v>68</v>
       </c>
@@ -3904,13 +3877,13 @@
       </c>
     </row>
     <row r="48" spans="2:4" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
     </row>
-    <row r="50" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B50" s="5" t="s">
         <v>70</v>
       </c>
@@ -3921,7 +3894,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="2:4" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B51" s="5" t="s">
         <v>72</v>
       </c>
@@ -3934,16 +3907,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B48:D48"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <conditionalFormatting sqref="C21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="notBetween">
@@ -4016,14 +3989,14 @@
       <c r="G3" s="20"/>
     </row>
     <row r="5" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
     </row>
     <row r="6" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
@@ -4764,14 +4737,14 @@
       </c>
     </row>
     <row r="9" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B10" s="5" t="s">
@@ -6250,14 +6223,14 @@
       </c>
     </row>
     <row r="15" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
     </row>
     <row r="16" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B16" s="5" t="s">
@@ -7856,14 +7829,14 @@
       </c>
     </row>
     <row r="21" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
     </row>
     <row r="22" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B22" s="5" t="s">
@@ -8604,14 +8577,14 @@
       </c>
     </row>
     <row r="25" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
     </row>
     <row r="26" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B26" s="5" t="s">
@@ -10459,14 +10432,14 @@
       </c>
     </row>
     <row r="32" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
     </row>
     <row r="33" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B33" s="5" t="s">
@@ -10838,14 +10811,14 @@
       </c>
     </row>
     <row r="35" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
     </row>
     <row r="36" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B36" s="5" t="s">
@@ -13293,14 +13266,14 @@
       </c>
     </row>
     <row r="42" spans="2:123" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
     </row>
     <row r="43" spans="2:123" x14ac:dyDescent="0.4">
       <c r="B43" s="1" t="s">
@@ -15140,16 +15113,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B42:G42"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B42:G42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -15161,7 +15134,7 @@
   <sheetPr>
     <tabColor rgb="FF2251FF"/>
   </sheetPr>
-  <dimension ref="B1:O40"/>
+  <dimension ref="B1:O28"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.73046875" customWidth="1"/>
@@ -15201,28 +15174,28 @@
       <c r="M2" s="20"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="E4" s="16" t="s">
+      <c r="C4" s="21"/>
+      <c r="E4" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="H4" s="16" t="s">
+      <c r="F4" s="21"/>
+      <c r="H4" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="I4" s="16"/>
-      <c r="K4" s="16" t="s">
+      <c r="I4" s="21"/>
+      <c r="K4" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="L4" s="16"/>
-      <c r="N4" s="16" t="s">
+      <c r="L4" s="21"/>
+      <c r="N4" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="O4" s="16"/>
+      <c r="O4" s="21"/>
     </row>
-    <row r="5" spans="2:15" s="24" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:15" s="15" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B5" s="22">
         <f ca="1">XIRR(NET_CASH_FLOW_UNLEVERED,CALENDAR_DATE)</f>
         <v>2.6807382702827457E-2</v>
@@ -15233,23 +15206,23 @@
         <v>-1.3886323571205138E-2</v>
       </c>
       <c r="F5" s="23"/>
-      <c r="H5" s="25">
+      <c r="H5" s="24">
         <f ca="1">SUMIF(NET_CASH_FLOW_LEVERED,"&gt;0",NET_CASH_FLOW_LEVERED)/-SUMIF(NET_CASH_FLOW_LEVERED,"&lt;0",NET_CASH_FLOW_LEVERED)</f>
         <v>0.97101609052064131</v>
       </c>
       <c r="I5" s="23"/>
-      <c r="K5" s="26">
+      <c r="K5" s="25">
         <f ca="1">ABS(MIN(CUMULATIVE_CASH_FLOW_LEVERED))</f>
         <v>7400959.6755597992</v>
       </c>
       <c r="L5" s="23"/>
-      <c r="N5" s="26" t="str">
+      <c r="N5" s="25" t="str">
         <f>IFERROR(AVERAGE(DSCR),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="O5" s="23"/>
     </row>
-    <row r="6" spans="2:15" s="24" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:15" s="15" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B6" s="23"/>
       <c r="C6" s="23"/>
       <c r="E6" s="23"/>
@@ -15262,211 +15235,42 @@
       <c r="O6" s="23"/>
     </row>
     <row r="9" spans="2:15" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
     </row>
-    <row r="28" spans="2:13" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="B28" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B29" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B30" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
+    <row r="27" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="28" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="14">
+    <mergeCell ref="B28:M28"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="N5:O6"/>
+    <mergeCell ref="B9:M9"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B4:C4"/>
@@ -15477,12 +15281,6 @@
     <mergeCell ref="H5:I6"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="K5:L6"/>
-    <mergeCell ref="B30:M40"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="N5:O6"/>
-    <mergeCell ref="B9:M9"/>
-    <mergeCell ref="B28:M28"/>
-    <mergeCell ref="B29:M29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
